--- a/doc/params/xplorer-params.xlsx
+++ b/doc/params/xplorer-params.xlsx
@@ -69814,7 +69814,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 17:34 UTC</t>
+          <t>2026-09-25 23:16 UTC</t>
         </is>
       </c>
     </row>
@@ -69826,7 +69826,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>561e54fe3b</t>
+          <t>630b8c0544</t>
         </is>
       </c>
     </row>
@@ -69850,7 +69850,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>xplorer-fw-v1.0.1-7-g561e54fe3b-dirty</t>
+          <t>xplorer-fw-v1.0.3</t>
         </is>
       </c>
     </row>
